--- a/datasets/day1_excel_foundations/08_pivottables_and_what_if_analysis/d1_m8_pivottables_answers.xlsx
+++ b/datasets/day1_excel_foundations/08_pivottables_and_what_if_analysis/d1_m8_pivottables_answers.xlsx
@@ -495,7 +495,7 @@
     <col width="22.5" customWidth="1" min="7" max="7"/>
     <col width="12.5" customWidth="1" min="8" max="8"/>
     <col width="10.5" customWidth="1" min="9" max="9"/>
-    <col width="9.5" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -635,7 +635,7 @@
         <v>1</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>119.7</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4">
@@ -679,7 +679,7 @@
         <v>2</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>3332</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="5">
@@ -723,7 +723,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1454.4</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="6">
@@ -767,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>806</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7">
@@ -811,7 +811,7 @@
         <v>2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1656</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="8">
@@ -855,7 +855,7 @@
         <v>3</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>326.25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -899,7 +899,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>779.2</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10">
@@ -943,7 +943,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>587.2</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11">
@@ -987,7 +987,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>801.6</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="12">
@@ -1031,7 +1031,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1663</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="13">
@@ -1075,7 +1075,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1037</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14">
@@ -1119,7 +1119,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>724</v>
+        <v>800</v>
       </c>
     </row>
     <row r="15">
@@ -1163,7 +1163,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>177</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -1207,7 +1207,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>653.8</v>
+        <v>800</v>
       </c>
     </row>
     <row r="17">
@@ -1251,7 +1251,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1758</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="18">
@@ -1295,7 +1295,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>56.1</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19">
@@ -1339,7 +1339,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1148</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="20">
@@ -1383,7 +1383,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>905.25</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="21">
@@ -1427,7 +1427,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>918</v>
+        <v>600</v>
       </c>
     </row>
     <row r="22">
@@ -1471,7 +1471,7 @@
         <v>3</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1806.9</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="23">
@@ -1515,7 +1515,7 @@
         <v>1</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>672.8</v>
+        <v>700</v>
       </c>
     </row>
     <row r="24">
@@ -1559,7 +1559,7 @@
         <v>2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>619.4</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25">
@@ -1603,7 +1603,7 @@
         <v>2</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>370</v>
+        <v>300</v>
       </c>
     </row>
     <row r="26">
@@ -1647,7 +1647,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>882</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="27">
@@ -1691,7 +1691,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>190.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -1735,7 +1735,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1696</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="29">
@@ -1779,7 +1779,7 @@
         <v>1</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>102.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -1823,7 +1823,7 @@
         <v>2</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>258.4</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31">
@@ -1867,7 +1867,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>263</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32">
@@ -1911,7 +1911,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>159</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33">
@@ -1955,7 +1955,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>352</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>148</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35">
@@ -2043,7 +2043,7 @@
         <v>2</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>226</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36">
@@ -2087,7 +2087,7 @@
         <v>1</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>289.85</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37">
@@ -2131,7 +2131,7 @@
         <v>1</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38">
@@ -2175,7 +2175,7 @@
         <v>4</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>4416</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="39">
@@ -2219,7 +2219,7 @@
         <v>2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>1160</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="40">
@@ -2263,7 +2263,7 @@
         <v>1</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>889.1</v>
+        <v>700</v>
       </c>
     </row>
     <row r="41">
@@ -2307,7 +2307,7 @@
         <v>1</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>115.9</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42">
@@ -2351,7 +2351,7 @@
         <v>1</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>303.05</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43">
@@ -2395,7 +2395,7 @@
         <v>1</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>710</v>
+        <v>800</v>
       </c>
     </row>
     <row r="44">
@@ -2439,7 +2439,7 @@
         <v>1</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>1245</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="45">
@@ -2483,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>1009.6</v>
+        <v>800</v>
       </c>
     </row>
     <row r="46">
@@ -2527,7 +2527,7 @@
         <v>1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>782</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="47">
@@ -2571,7 +2571,7 @@
         <v>1</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>174</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48">
@@ -2615,7 +2615,7 @@
         <v>3</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>396</v>
+        <v>240</v>
       </c>
     </row>
     <row r="49">
@@ -2659,7 +2659,7 @@
         <v>1</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>1799</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="50">
@@ -2703,7 +2703,7 @@
         <v>1</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>1259</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="51">
@@ -2747,7 +2747,7 @@
         <v>1</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>146</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52">
@@ -2791,7 +2791,7 @@
         <v>4</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>3980</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="53">
@@ -2835,7 +2835,7 @@
         <v>1</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>1003</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="54">
@@ -2879,7 +2879,7 @@
         <v>1</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>794</v>
+        <v>900</v>
       </c>
     </row>
     <row r="55">
@@ -2923,7 +2923,7 @@
         <v>4</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>6777.6</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="56">
@@ -2967,7 +2967,7 @@
         <v>3</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>2898</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="57">
@@ -3011,7 +3011,7 @@
         <v>2</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>214</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58">
@@ -3055,7 +3055,7 @@
         <v>1</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>165.3</v>
+        <v>120</v>
       </c>
     </row>
     <row r="59">
@@ -3099,7 +3099,7 @@
         <v>1</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60">
@@ -3143,7 +3143,7 @@
         <v>2</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>2759.4</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="61">
@@ -3187,7 +3187,7 @@
         <v>3</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>1050</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="62">
@@ -3231,7 +3231,7 @@
         <v>1</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="63">
@@ -3275,7 +3275,7 @@
         <v>1</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>1928</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="64">
@@ -3319,7 +3319,7 @@
         <v>1</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>765</v>
+        <v>700</v>
       </c>
     </row>
     <row r="65">
@@ -3363,7 +3363,7 @@
         <v>2</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>212</v>
+        <v>100</v>
       </c>
     </row>
     <row r="66">
@@ -3407,7 +3407,7 @@
         <v>1</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>1581</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="67">
@@ -3451,7 +3451,7 @@
         <v>1</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>1433</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="68">
@@ -3495,7 +3495,7 @@
         <v>1</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>1737</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="69">
@@ -3539,7 +3539,7 @@
         <v>1</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>812</v>
+        <v>700</v>
       </c>
     </row>
     <row r="70">
@@ -3583,7 +3583,7 @@
         <v>1</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>1244</v>
+        <v>900</v>
       </c>
     </row>
     <row r="71">
@@ -3627,7 +3627,7 @@
         <v>1</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>312</v>
+        <v>150</v>
       </c>
     </row>
     <row r="72">
@@ -3671,7 +3671,7 @@
         <v>2</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>2561.4</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="73">
@@ -3715,7 +3715,7 @@
         <v>1</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>645</v>
+        <v>500</v>
       </c>
     </row>
     <row r="74">
@@ -3759,7 +3759,7 @@
         <v>1</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>548.25</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="75">
@@ -3803,7 +3803,7 @@
         <v>1</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>43.2</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76">
@@ -3847,7 +3847,7 @@
         <v>1</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="77">
@@ -3891,7 +3891,7 @@
         <v>1</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>1996</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="78">
@@ -3935,7 +3935,7 @@
         <v>1</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>1608.35</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="79">
@@ -3979,7 +3979,7 @@
         <v>1</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>848</v>
+        <v>800</v>
       </c>
     </row>
     <row r="80">
@@ -4023,7 +4023,7 @@
         <v>1</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>94.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81">
@@ -4067,7 +4067,7 @@
         <v>1</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>135</v>
+        <v>60</v>
       </c>
     </row>
     <row r="82">
@@ -4111,7 +4111,7 @@
         <v>4</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>2052</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="83">
@@ -4155,7 +4155,7 @@
         <v>1</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>1138</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="84">
@@ -4199,7 +4199,7 @@
         <v>2</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>1310</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="85">
@@ -4243,7 +4243,7 @@
         <v>1</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>949</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="86">
@@ -4287,7 +4287,7 @@
         <v>2</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>812</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="87">
@@ -4331,7 +4331,7 @@
         <v>2</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>154</v>
+        <v>240</v>
       </c>
     </row>
     <row r="88">
@@ -4375,7 +4375,7 @@
         <v>1</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89">
@@ -4419,7 +4419,7 @@
         <v>1</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>126</v>
+        <v>100</v>
       </c>
     </row>
     <row r="90">
@@ -4463,7 +4463,7 @@
         <v>1</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>105</v>
+        <v>200</v>
       </c>
     </row>
     <row r="91">
@@ -4507,7 +4507,7 @@
         <v>1</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>856</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="92">
@@ -4551,7 +4551,7 @@
         <v>3</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>1638.9</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="93">
@@ -4595,7 +4595,7 @@
         <v>2</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>254</v>
+        <v>160</v>
       </c>
     </row>
     <row r="94">
@@ -4639,7 +4639,7 @@
         <v>4</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>2385.6</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="95">
@@ -4683,7 +4683,7 @@
         <v>1</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>693.7</v>
+        <v>500</v>
       </c>
     </row>
     <row r="96">
@@ -4727,7 +4727,7 @@
         <v>2</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>3236</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="97">
@@ -4771,7 +4771,7 @@
         <v>3</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>2706</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="98">
@@ -4815,7 +4815,7 @@
         <v>1</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>1538</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="99">
@@ -4859,7 +4859,7 @@
         <v>1</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>114.75</v>
+        <v>150</v>
       </c>
     </row>
     <row r="100">
@@ -4903,7 +4903,7 @@
         <v>2</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>56</v>
+        <v>240</v>
       </c>
     </row>
     <row r="101">
@@ -4947,7 +4947,7 @@
         <v>1</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>33.6</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Goal Seek target for Step 12: set B13 to 18000 by changing B5 (answer is about 12.6%).</t>
+          <t>Goal Seek target for Step 12: set B13 to 16000 by changing B5 (answer is about 10%).</t>
         </is>
       </c>
     </row>

--- a/datasets/day1_excel_foundations/08_pivottables_and_what_if_analysis/d1_m8_pivottables_answers.xlsx
+++ b/datasets/day1_excel_foundations/08_pivottables_and_what_if_analysis/d1_m8_pivottables_answers.xlsx
@@ -18,12 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -101,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -113,10 +112,8 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1636,140 +1633,94 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="21.5" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>NovaTech Retail - Next Year Projection</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>INPUTS (change the yellow cells)</t>
-        </is>
-      </c>
-    </row>
+          <t>Sales Target Planner</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Everything below is on this What-If sheet - no other sheet is involved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>Current Annual Revenue</t>
-        </is>
-      </c>
-      <c r="B4" s="9">
-        <f>SUM(Orders!J2:J21)</f>
-        <v/>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Goal Seek target for Step 12: set B13 to 3000 by changing B5 (answer is about 7%).</t>
+          <t>Laptops to sell</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>GOAL SEEK: we want Total Sales (B7) to reach 10000.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Price Increase</t>
+          <t>Price each</t>
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Note the results depend on each other: Revenue feeds Costs, both feed Profit.</t>
+        <v>1000</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Data tab &gt; What-If Analysis &gt; Goal Seek:</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Expected Volume Change</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="n">
-        <v>-0.02</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Set cell:     B7   (Total sales - the formula)</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Cost as % of Revenue</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="n">
-        <v>0.62</v>
+          <t>Total sales</t>
+        </is>
+      </c>
+      <c r="B7" s="11">
+        <f>B4*B5</f>
+        <v/>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   To value:     10000</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Fixed Costs</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="n">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>RESULTS (calculated - do not type over these)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Projected Revenue</t>
-        </is>
-      </c>
-      <c r="B11" s="12">
-        <f>B4*(1+B5)*(1+B6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Projected Costs</t>
-        </is>
-      </c>
-      <c r="B12" s="12">
-        <f>B11*B7+B8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Projected Profit</t>
-        </is>
-      </c>
-      <c r="B13" s="12">
-        <f>B11-B12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Profit Margin</t>
-        </is>
-      </c>
-      <c r="B14" s="13">
-        <f>IFERROR(B13/B11,0)</f>
-        <v/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   By changing:  B4   (Laptops to sell - a plain number)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Excel works backwards and puts 10 in B4  (because 10 x 1000 = 10000).</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/datasets/day1_excel_foundations/08_pivottables_and_what_if_analysis/d1_m8_pivottables_answers.xlsx
+++ b/datasets/day1_excel_foundations/08_pivottables_and_what_if_analysis/d1_m8_pivottables_answers.xlsx
@@ -18,11 +18,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -51,7 +52,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +72,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -100,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +121,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1633,11 +1641,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="21.5" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1723,6 +1732,73 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>NOW WITH REAL DATA - an answer you could not work out in your head</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Current total sales</t>
+        </is>
+      </c>
+      <c r="B12" s="12">
+        <f>SUM(Orders!J2:J21)</f>
+        <v/>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>&lt;- adds the Sales column on the Orders sheet</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>GOAL SEEK 2: we want Projected total (B14) to reach 20000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Sales growth</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Set cell: B14    To value: 20000    By changing: B13 (Sales growth)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Projected total</t>
+        </is>
+      </c>
+      <c r="B14" s="11">
+        <f>B12*(1+B13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Excel finds about 13.4% - a number you could not have guessed. THAT is</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>when Goal Seek really earns its keep: real numbers, no easy mental maths.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
